--- a/feedback_forms/010_customer_communication_preference_questionnaire--feedback_forms.xlsx
+++ b/feedback_forms/010_customer_communication_preference_questionnaire--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -698,7 +698,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Communication Channels</t>
+          <t>Communication Channels Text</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Preferred Contact Time</t>
+          <t>Preferred Contact Time Text</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Preferred Contact Method</t>
+          <t>Preferred Contact Method Text</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Preferred Contact Frequency</t>
+          <t>Preferred Contact Frequency Text</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Preferred Contact Days</t>
+          <t>Preferred Contact Days Text</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -842,8 +842,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,12 +905,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Text Message'}</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
